--- a/samples/수주취합/2026.09.29_직송 인천엔진.xlsx
+++ b/samples/수주취합/2026.09.29_직송 인천엔진.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="91">
   <si>
     <t>No</t>
   </si>
@@ -298,6 +298,9 @@
   </si>
   <si>
     <t>EA</t>
+  </si>
+  <si>
+    <t>KRW</t>
   </si>
   <si>
     <t>Z1</t>
@@ -1002,11 +1005,11 @@
       <c r="AA2" s="1">
         <v>46285.000601851854</v>
       </c>
-      <c r="AB2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>81</v>
+      <c r="AB2">
+        <v>900</v>
+      </c>
+      <c r="AC2">
+        <v>27000</v>
       </c>
       <c r="AD2" t="s">
         <v>88</v>
@@ -1015,7 +1018,7 @@
         <v>81</v>
       </c>
       <c r="AF2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AG2" t="s">
         <v>81</v>
@@ -1057,7 +1060,7 @@
         <v>81</v>
       </c>
       <c r="AT2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AU2" t="s">
         <v>81</v>
